--- a/talend_input/CPEMS_FGHPC_PNTBNG_OCC_20260127.xlsx
+++ b/talend_input/CPEMS_FGHPC_PNTBNG_OCC_20260127.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\GitHub\FGEN\cpems-automation-talend-training\talend_input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CF242E1-83F7-4311-AD94-E0612DB3BE6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{86D168F4-B5E6-4619-9C2C-D9CFFABCDE4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="2295" windowWidth="21600" windowHeight="11295" xr2:uid="{03103E4E-B89F-4A28-8185-2741B79616A3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{828220A4-B4E7-48BE-9469-7C473421211A}"/>
   </bookViews>
   <sheets>
     <sheet name="CPEMS_FGHPC_PNTBNG_OCC_20260127" sheetId="1" r:id="rId1"/>
@@ -89,9 +89,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd\ h:mm"/>
-  </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -571,7 +568,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -926,12 +923,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{876870DC-77D2-4C11-8A95-E9BDEDBC0FE5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68E9E9A1-9C52-4362-8D7A-3EF4AFB97434}">
   <dimension ref="A1:O49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="5" max="5" width="15.5703125" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
